--- a/minah-tekstil/trendyol/minah-trendyol-dosya-2.xlsx
+++ b/minah-tekstil/trendyol/minah-trendyol-dosya-2.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5422" uniqueCount="3466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5422" uniqueCount="3467">
   <si>
     <t>Barkod</t>
   </si>
@@ -10260,6 +10260,9 @@
   </si>
   <si>
     <t>MNH-POLO-TRIKO-KAZAK</t>
+  </si>
+  <si>
+    <t>ixoskids club</t>
   </si>
   <si>
     <t>Kadın Turuncu Polo Yaka Siyah Beyaz Çizgili Triko Kazak</t>
@@ -40390,7 +40393,7 @@
         <v>3327</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D2" t="s">
         <v>360</v>
@@ -40399,10 +40402,10 @@
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3328</v>
+        <v>3329</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="H2" s="38">
         <v>950</v>
@@ -40464,13 +40467,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="B3" t="s">
         <v>3327</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="s">
         <v>360</v>
@@ -40482,7 +40485,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3331</v>
+        <v>3332</v>
       </c>
       <c r="H3" s="38">
         <v>950</v>
@@ -40494,7 +40497,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3330</v>
+        <v>3331</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -40524,7 +40527,7 @@
         <v>79</v>
       </c>
       <c r="AQ3" t="s">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="AS3" t="s">
         <v>164</v>
@@ -40544,13 +40547,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="B4" t="s">
         <v>3327</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D4" t="s">
         <v>360</v>
@@ -40562,7 +40565,7 @@
         <v>97</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3334</v>
+        <v>3335</v>
       </c>
       <c r="H4" s="38">
         <v>950</v>
@@ -40574,7 +40577,7 @@
         <v>5</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3333</v>
+        <v>3334</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -40601,7 +40604,7 @@
         <v>79</v>
       </c>
       <c r="AQ4" t="s">
-        <v>3335</v>
+        <v>3336</v>
       </c>
       <c r="AS4" t="s">
         <v>164</v>
@@ -40621,13 +40624,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="B5" t="s">
         <v>3327</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D5" t="s">
         <v>360</v>
@@ -40636,10 +40639,10 @@
         <v>70</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>3337</v>
+        <v>3338</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3338</v>
+        <v>3339</v>
       </c>
       <c r="H5" s="38">
         <v>950</v>
@@ -40651,7 +40654,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3336</v>
+        <v>3337</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -40681,7 +40684,7 @@
         <v>79</v>
       </c>
       <c r="AQ5" t="s">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="AS5" t="s">
         <v>164</v>
@@ -40701,13 +40704,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="B6" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D6" t="s">
         <v>360</v>
@@ -40716,10 +40719,10 @@
         <v>70</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3343</v>
+        <v>3344</v>
       </c>
       <c r="H6" s="38">
         <v>800</v>
@@ -40731,7 +40734,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -40781,13 +40784,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="B7" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="s">
         <v>360</v>
@@ -40796,10 +40799,10 @@
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3345</v>
+        <v>3346</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="H7" s="38">
         <v>800</v>
@@ -40811,7 +40814,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3344</v>
+        <v>3345</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -40858,13 +40861,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="B8" t="s">
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D8" t="s">
         <v>360</v>
@@ -40873,10 +40876,10 @@
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3348</v>
+        <v>3349</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3349</v>
+        <v>3350</v>
       </c>
       <c r="H8" s="38">
         <v>800</v>
@@ -40888,7 +40891,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -40938,13 +40941,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="B9" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D9" t="s">
         <v>360</v>
@@ -40953,10 +40956,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="H9" s="38">
         <v>1040</v>
@@ -40968,7 +40971,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3350</v>
+        <v>3351</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -41015,13 +41018,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="B10" t="s">
-        <v>3351</v>
+        <v>3352</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D10" t="s">
         <v>360</v>
@@ -41030,10 +41033,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3356</v>
+        <v>3357</v>
       </c>
       <c r="H10" s="38">
         <v>1040</v>
@@ -41045,7 +41048,7 @@
         <v>20</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3354</v>
+        <v>3355</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -41092,13 +41095,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="B11" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D11" t="s">
         <v>360</v>
@@ -41107,10 +41110,10 @@
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3359</v>
+        <v>3360</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3360</v>
+        <v>3361</v>
       </c>
       <c r="H11" s="38">
         <v>900</v>
@@ -41122,7 +41125,7 @@
         <v>5</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3357</v>
+        <v>3358</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -41152,7 +41155,7 @@
         <v>79</v>
       </c>
       <c r="AQ11" t="s">
-        <v>3361</v>
+        <v>3362</v>
       </c>
       <c r="AS11" t="s">
         <v>164</v>
@@ -41172,13 +41175,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="B12" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D12" t="s">
         <v>360</v>
@@ -41187,10 +41190,10 @@
         <v>70</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="H12" s="38">
         <v>900</v>
@@ -41202,7 +41205,7 @@
         <v>5</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3362</v>
+        <v>3363</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -41232,7 +41235,7 @@
         <v>79</v>
       </c>
       <c r="AQ12" t="s">
-        <v>3365</v>
+        <v>3366</v>
       </c>
       <c r="AS12" t="s">
         <v>164</v>
@@ -41252,13 +41255,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="B13" t="s">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D13" t="s">
         <v>360</v>
@@ -41267,10 +41270,10 @@
         <v>70</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>3367</v>
+        <v>3368</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3368</v>
+        <v>3369</v>
       </c>
       <c r="H13" s="38">
         <v>900</v>
@@ -41282,7 +41285,7 @@
         <v>5</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3366</v>
+        <v>3367</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -41309,7 +41312,7 @@
         <v>79</v>
       </c>
       <c r="AQ13" t="s">
-        <v>3369</v>
+        <v>3370</v>
       </c>
       <c r="AS13" t="s">
         <v>164</v>
@@ -43294,13 +43297,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="B2" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D2" t="s">
         <v>357</v>
@@ -43309,10 +43312,10 @@
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="H2" s="38">
         <v>850</v>
@@ -43324,7 +43327,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3370</v>
+        <v>3371</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -43374,13 +43377,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="B3" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="s">
         <v>357</v>
@@ -43389,10 +43392,10 @@
         <v>70</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="H3" s="38">
         <v>850</v>
@@ -43404,7 +43407,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -43454,13 +43457,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="B4" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D4" t="s">
         <v>357</v>
@@ -43469,10 +43472,10 @@
         <v>70</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="H4" s="38">
         <v>850</v>
@@ -43484,7 +43487,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3375</v>
+        <v>3376</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -43534,13 +43537,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="B5" t="s">
-        <v>3371</v>
+        <v>3372</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D5" t="s">
         <v>357</v>
@@ -43549,10 +43552,10 @@
         <v>70</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="H5" s="38">
         <v>850</v>
@@ -43564,7 +43567,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -43614,13 +43617,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="B6" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D6" t="s">
         <v>357</v>
@@ -43629,10 +43632,10 @@
         <v>70</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="H6" s="38">
         <v>1050</v>
@@ -43644,7 +43647,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3377</v>
+        <v>3378</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -43691,13 +43694,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="B7" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="s">
         <v>357</v>
@@ -43706,10 +43709,10 @@
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="H7" s="38">
         <v>1050</v>
@@ -43721,7 +43724,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3381</v>
+        <v>3382</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -43768,13 +43771,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="B8" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D8" t="s">
         <v>357</v>
@@ -43783,10 +43786,10 @@
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="H8" s="38">
         <v>1050</v>
@@ -43798,7 +43801,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3382</v>
+        <v>3383</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -43845,13 +43848,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="B9" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D9" t="s">
         <v>357</v>
@@ -43860,10 +43863,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="H9" s="38">
         <v>1050</v>
@@ -43875,7 +43878,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3383</v>
+        <v>3384</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -43922,13 +43925,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="B10" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D10" t="s">
         <v>357</v>
@@ -43937,10 +43940,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3379</v>
+        <v>3380</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3380</v>
+        <v>3381</v>
       </c>
       <c r="H10" s="38">
         <v>1050</v>
@@ -43952,7 +43955,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -43999,13 +44002,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="B11" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D11" t="s">
         <v>357</v>
@@ -44014,10 +44017,10 @@
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="H11" s="38">
         <v>1050</v>
@@ -44029,7 +44032,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3385</v>
+        <v>3386</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -44076,13 +44079,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="B12" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D12" t="s">
         <v>357</v>
@@ -44091,10 +44094,10 @@
         <v>70</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="H12" s="38">
         <v>1050</v>
@@ -44106,7 +44109,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3388</v>
+        <v>3389</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -44153,13 +44156,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="B13" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D13" t="s">
         <v>357</v>
@@ -44168,10 +44171,10 @@
         <v>70</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="H13" s="38">
         <v>1050</v>
@@ -44183,7 +44186,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3389</v>
+        <v>3390</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -44230,13 +44233,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="B14" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D14" t="s">
         <v>357</v>
@@ -44245,10 +44248,10 @@
         <v>70</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="H14" s="38">
         <v>1050</v>
@@ -44260,7 +44263,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="L14" s="39">
         <v>10</v>
@@ -44307,13 +44310,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="B15" t="s">
-        <v>3378</v>
+        <v>3379</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D15" t="s">
         <v>357</v>
@@ -44322,10 +44325,10 @@
         <v>70</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>3386</v>
+        <v>3387</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>3387</v>
+        <v>3388</v>
       </c>
       <c r="H15" s="38">
         <v>1050</v>
@@ -44337,7 +44340,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>3391</v>
+        <v>3392</v>
       </c>
       <c r="L15" s="39">
         <v>10</v>
@@ -46349,13 +46352,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="B2" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -46367,7 +46370,7 @@
         <v>183</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="H2" s="38">
         <v>799</v>
@@ -46379,7 +46382,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -46429,13 +46432,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="B3" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -46447,7 +46450,7 @@
         <v>183</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="H3" s="38">
         <v>799</v>
@@ -46459,7 +46462,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -46509,13 +46512,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="B4" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -46527,7 +46530,7 @@
         <v>183</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="H4" s="38">
         <v>799</v>
@@ -46539,7 +46542,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -46589,13 +46592,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="B5" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -46607,7 +46610,7 @@
         <v>183</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="H5" s="38">
         <v>799</v>
@@ -46619,7 +46622,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3397</v>
+        <v>3398</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -46669,13 +46672,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="B6" t="s">
-        <v>3393</v>
+        <v>3394</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -46687,7 +46690,7 @@
         <v>183</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3394</v>
+        <v>3395</v>
       </c>
       <c r="H6" s="38">
         <v>799</v>
@@ -46699,7 +46702,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -46749,13 +46752,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="B7" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -46764,10 +46767,10 @@
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="H7" s="38">
         <v>785</v>
@@ -46779,7 +46782,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -46829,13 +46832,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="B8" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -46844,10 +46847,10 @@
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="H8" s="38">
         <v>785</v>
@@ -46859,7 +46862,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3403</v>
+        <v>3404</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -46909,13 +46912,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="B9" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -46924,10 +46927,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="H9" s="38">
         <v>785</v>
@@ -46939,7 +46942,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -46989,13 +46992,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="B10" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D10" t="s">
         <v>333</v>
@@ -47004,10 +47007,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="H10" s="38">
         <v>785</v>
@@ -47019,7 +47022,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3405</v>
+        <v>3406</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -47069,13 +47072,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="B11" t="s">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D11" t="s">
         <v>333</v>
@@ -47084,10 +47087,10 @@
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3402</v>
+        <v>3403</v>
       </c>
       <c r="H11" s="38">
         <v>785</v>
@@ -47099,7 +47102,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3406</v>
+        <v>3407</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -47149,13 +47152,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="B12" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D12" t="s">
         <v>333</v>
@@ -47167,7 +47170,7 @@
         <v>265</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="H12" s="38">
         <v>800</v>
@@ -47179,7 +47182,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -47226,13 +47229,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="B13" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D13" t="s">
         <v>333</v>
@@ -47244,7 +47247,7 @@
         <v>265</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="H13" s="38">
         <v>800</v>
@@ -47256,7 +47259,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -47303,13 +47306,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="B14" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D14" t="s">
         <v>333</v>
@@ -47321,7 +47324,7 @@
         <v>265</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="H14" s="38">
         <v>800</v>
@@ -47333,7 +47336,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>3411</v>
+        <v>3412</v>
       </c>
       <c r="L14" s="39">
         <v>10</v>
@@ -47380,13 +47383,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="B15" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D15" t="s">
         <v>333</v>
@@ -47398,7 +47401,7 @@
         <v>265</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="H15" s="38">
         <v>800</v>
@@ -47410,7 +47413,7 @@
         <v>2</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>3412</v>
+        <v>3413</v>
       </c>
       <c r="L15" s="39">
         <v>10</v>
@@ -47457,13 +47460,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="B16" t="s">
-        <v>3408</v>
+        <v>3409</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D16" t="s">
         <v>333</v>
@@ -47475,7 +47478,7 @@
         <v>265</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>3409</v>
+        <v>3410</v>
       </c>
       <c r="H16" s="38">
         <v>800</v>
@@ -47487,7 +47490,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>3413</v>
+        <v>3414</v>
       </c>
       <c r="L16" s="39">
         <v>10</v>
@@ -49499,25 +49502,25 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="B2" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D2" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="H2" s="38">
         <v>500</v>
@@ -49529,7 +49532,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -49579,25 +49582,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="B3" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E3" t="s">
         <v>70</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="H3" s="38">
         <v>500</v>
@@ -49609,7 +49612,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -49659,25 +49662,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="B4" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D4" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E4" t="s">
         <v>70</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="H4" s="38">
         <v>500</v>
@@ -49689,7 +49692,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3420</v>
+        <v>3421</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -49739,25 +49742,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="B5" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D5" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="H5" s="38">
         <v>500</v>
@@ -49769,7 +49772,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3421</v>
+        <v>3422</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -49819,25 +49822,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="B6" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D6" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E6" t="s">
         <v>70</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="H6" s="38">
         <v>500</v>
@@ -49849,7 +49852,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3422</v>
+        <v>3423</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -49899,25 +49902,25 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="B7" t="s">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E7" t="s">
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="H7" s="38">
         <v>500</v>
@@ -49929,7 +49932,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3423</v>
+        <v>3424</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -49979,25 +49982,25 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="B8" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D8" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E8" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="H8" s="38">
         <v>500</v>
@@ -50009,7 +50012,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3424</v>
+        <v>3425</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -50053,25 +50056,25 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="B9" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D9" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E9" t="s">
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="H9" s="38">
         <v>500</v>
@@ -50083,7 +50086,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -50127,25 +50130,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="B10" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D10" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E10" t="s">
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="H10" s="38">
         <v>500</v>
@@ -50157,7 +50160,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -50201,25 +50204,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="B11" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D11" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E11" t="s">
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="H11" s="38">
         <v>500</v>
@@ -50231,7 +50234,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -50275,25 +50278,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="B12" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D12" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E12" t="s">
         <v>70</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="H12" s="38">
         <v>500</v>
@@ -50305,7 +50308,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3431</v>
+        <v>3432</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -50349,25 +50352,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="B13" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D13" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E13" t="s">
         <v>70</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>3426</v>
+        <v>3427</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3427</v>
+        <v>3428</v>
       </c>
       <c r="H13" s="38">
         <v>500</v>
@@ -50379,7 +50382,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3432</v>
+        <v>3433</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -50423,25 +50426,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="B14" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D14" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="H14" s="38">
         <v>550</v>
@@ -50453,7 +50456,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>3433</v>
+        <v>3434</v>
       </c>
       <c r="L14" s="39">
         <v>10</v>
@@ -50503,25 +50506,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="B15" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D15" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E15" t="s">
         <v>70</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="H15" s="38">
         <v>550</v>
@@ -50533,7 +50536,7 @@
         <v>2</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="L15" s="39">
         <v>10</v>
@@ -50583,25 +50586,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="B16" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D16" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E16" t="s">
         <v>70</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="H16" s="38">
         <v>550</v>
@@ -50613,7 +50616,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="L16" s="39">
         <v>10</v>
@@ -50663,25 +50666,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="B17" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D17" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E17" t="s">
         <v>70</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="H17" s="38">
         <v>550</v>
@@ -50693,7 +50696,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>3438</v>
+        <v>3439</v>
       </c>
       <c r="L17" s="39">
         <v>10</v>
@@ -50743,25 +50746,25 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="B18" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D18" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E18" t="s">
         <v>70</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="H18" s="38">
         <v>550</v>
@@ -50773,7 +50776,7 @@
         <v>2</v>
       </c>
       <c r="K18" s="39" t="s">
-        <v>3439</v>
+        <v>3440</v>
       </c>
       <c r="L18" s="39">
         <v>10</v>
@@ -50823,25 +50826,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="B19" t="s">
-        <v>3425</v>
+        <v>3426</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D19" t="s">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="E19" t="s">
         <v>70</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>3435</v>
+        <v>3436</v>
       </c>
       <c r="H19" s="38">
         <v>550</v>
@@ -50853,7 +50856,7 @@
         <v>2</v>
       </c>
       <c r="K19" s="39" t="s">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="L19" s="39">
         <v>10</v>
@@ -52883,13 +52886,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="B2" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D2" t="s">
         <v>375</v>
@@ -52901,7 +52904,7 @@
         <v>361</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="H2" s="38">
         <v>250</v>
@@ -52913,7 +52916,7 @@
         <v>8</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3441</v>
+        <v>3442</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -52960,13 +52963,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="B3" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="s">
         <v>375</v>
@@ -52978,7 +52981,7 @@
         <v>361</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="H3" s="38">
         <v>250</v>
@@ -52990,7 +52993,7 @@
         <v>8</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -53037,13 +53040,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="B4" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D4" t="s">
         <v>375</v>
@@ -53055,7 +53058,7 @@
         <v>361</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="H4" s="38">
         <v>250</v>
@@ -53067,7 +53070,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3445</v>
+        <v>3446</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -53114,13 +53117,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="B5" t="s">
-        <v>3442</v>
+        <v>3443</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D5" t="s">
         <v>375</v>
@@ -53132,7 +53135,7 @@
         <v>361</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="H5" s="38">
         <v>250</v>
@@ -53144,7 +53147,7 @@
         <v>8</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3446</v>
+        <v>3447</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -55156,13 +55159,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="B2" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D2" t="s">
         <v>349</v>
@@ -55174,7 +55177,7 @@
         <v>520</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="H2" s="38">
         <v>1600</v>
@@ -55186,7 +55189,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3447</v>
+        <v>3448</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -55233,13 +55236,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="B3" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="s">
         <v>349</v>
@@ -55251,7 +55254,7 @@
         <v>520</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="H3" s="38">
         <v>1600</v>
@@ -55263,7 +55266,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -55310,13 +55313,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="B4" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D4" t="s">
         <v>349</v>
@@ -55328,7 +55331,7 @@
         <v>520</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="H4" s="38">
         <v>1600</v>
@@ -55340,7 +55343,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -55387,13 +55390,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="B5" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D5" t="s">
         <v>349</v>
@@ -55405,7 +55408,7 @@
         <v>520</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3449</v>
+        <v>3450</v>
       </c>
       <c r="H5" s="38">
         <v>1600</v>
@@ -55417,7 +55420,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -55464,13 +55467,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="B6" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D6" t="s">
         <v>349</v>
@@ -55482,7 +55485,7 @@
         <v>533</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="H6" s="38">
         <v>1600</v>
@@ -55494,7 +55497,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -55544,13 +55547,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="B7" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D7" t="s">
         <v>349</v>
@@ -55562,7 +55565,7 @@
         <v>533</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="H7" s="38">
         <v>1600</v>
@@ -55574,7 +55577,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -55624,13 +55627,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="B8" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D8" t="s">
         <v>349</v>
@@ -55642,7 +55645,7 @@
         <v>533</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="H8" s="38">
         <v>1600</v>
@@ -55654,7 +55657,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -55704,13 +55707,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="B9" t="s">
-        <v>3448</v>
+        <v>3449</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D9" t="s">
         <v>349</v>
@@ -55722,7 +55725,7 @@
         <v>533</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3454</v>
+        <v>3455</v>
       </c>
       <c r="H9" s="38">
         <v>1600</v>
@@ -55734,7 +55737,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -57749,25 +57752,25 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="B2" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D2" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3462</v>
+        <v>3463</v>
       </c>
       <c r="H2" s="38">
         <v>1000</v>
@@ -57779,7 +57782,7 @@
         <v>5</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3458</v>
+        <v>3459</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -57820,25 +57823,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="B3" t="s">
-        <v>3459</v>
+        <v>3460</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>3328</v>
       </c>
       <c r="D3" t="s">
-        <v>3460</v>
+        <v>3461</v>
       </c>
       <c r="E3" t="s">
         <v>70</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>3464</v>
+        <v>3465</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3465</v>
+        <v>3466</v>
       </c>
       <c r="H3" s="38">
         <v>1000</v>
@@ -57850,7 +57853,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3463</v>
+        <v>3464</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>

--- a/minah-tekstil/trendyol/minah-trendyol-dosya-2.xlsx
+++ b/minah-tekstil/trendyol/minah-trendyol-dosya-2.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7117" uniqueCount="3467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7140" uniqueCount="3470">
   <si>
     <t>Barkod</t>
   </si>
@@ -10254,6 +10254,15 @@
   </si>
   <si>
     <t>Bu alanda "Hızlı Teslimat" ve "Bugün Kargoda" değişkenlerini ekleyebilirsiniz.</t>
+  </si>
+  <si>
+    <t>Parça Sayısı</t>
+  </si>
+  <si>
+    <t>Astar Durumu</t>
+  </si>
+  <si>
+    <t>Kalınlık</t>
   </si>
   <si>
     <t>MNH-POLO-TRIKO-KAZAK-TURUNCU-STD</t>
@@ -40198,7 +40207,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV13"/>
+  <dimension ref="A1:BY13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -40441,16 +40450,25 @@
       <c r="BV1" s="41" t="s">
         <v>1846</v>
       </c>
+      <c r="BW1" s="41" t="s">
+        <v>3326</v>
+      </c>
+      <c r="BX1" s="41" t="s">
+        <v>3327</v>
+      </c>
+      <c r="BY1" s="41" t="s">
+        <v>3328</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3326</v>
+        <v>3329</v>
       </c>
       <c r="B2" t="s">
-        <v>3327</v>
+        <v>3330</v>
       </c>
       <c r="C2" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D2" t="s">
         <v>360</v>
@@ -40459,10 +40477,10 @@
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3329</v>
+        <v>3332</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3330</v>
+        <v>3333</v>
       </c>
       <c r="H2" s="38">
         <v>950</v>
@@ -40474,7 +40492,7 @@
         <v>5</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3326</v>
+        <v>3329</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -40527,13 +40545,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3330</v>
+      </c>
+      <c r="C3" t="s">
         <v>3331</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3327</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3328</v>
       </c>
       <c r="D3" t="s">
         <v>360</v>
@@ -40545,7 +40563,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3332</v>
+        <v>3335</v>
       </c>
       <c r="H3" s="38">
         <v>950</v>
@@ -40557,7 +40575,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3331</v>
+        <v>3334</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -40590,7 +40608,7 @@
         <v>830</v>
       </c>
       <c r="AZ3" t="s">
-        <v>3333</v>
+        <v>3336</v>
       </c>
       <c r="BC3" t="s">
         <v>164</v>
@@ -40610,13 +40628,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3334</v>
+        <v>3337</v>
       </c>
       <c r="B4" t="s">
-        <v>3327</v>
+        <v>3330</v>
       </c>
       <c r="C4" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D4" t="s">
         <v>360</v>
@@ -40628,7 +40646,7 @@
         <v>97</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3335</v>
+        <v>3338</v>
       </c>
       <c r="H4" s="38">
         <v>950</v>
@@ -40640,7 +40658,7 @@
         <v>5</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3334</v>
+        <v>3337</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -40670,7 +40688,7 @@
         <v>830</v>
       </c>
       <c r="AZ4" t="s">
-        <v>3336</v>
+        <v>3339</v>
       </c>
       <c r="BC4" t="s">
         <v>164</v>
@@ -40690,13 +40708,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3337</v>
+        <v>3340</v>
       </c>
       <c r="B5" t="s">
-        <v>3327</v>
+        <v>3330</v>
       </c>
       <c r="C5" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D5" t="s">
         <v>360</v>
@@ -40705,10 +40723,10 @@
         <v>70</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>3338</v>
+        <v>3341</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3339</v>
+        <v>3342</v>
       </c>
       <c r="H5" s="38">
         <v>950</v>
@@ -40720,7 +40738,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3337</v>
+        <v>3340</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -40753,7 +40771,7 @@
         <v>830</v>
       </c>
       <c r="AZ5" t="s">
-        <v>3340</v>
+        <v>3343</v>
       </c>
       <c r="BC5" t="s">
         <v>164</v>
@@ -40773,13 +40791,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3341</v>
+        <v>3344</v>
       </c>
       <c r="B6" t="s">
-        <v>3342</v>
+        <v>3345</v>
       </c>
       <c r="C6" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D6" t="s">
         <v>360</v>
@@ -40788,10 +40806,10 @@
         <v>70</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>3343</v>
+        <v>3346</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3344</v>
+        <v>3347</v>
       </c>
       <c r="H6" s="38">
         <v>800</v>
@@ -40803,7 +40821,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3341</v>
+        <v>3344</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -40856,13 +40874,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>3348</v>
+      </c>
+      <c r="B7" t="s">
         <v>3345</v>
       </c>
-      <c r="B7" t="s">
-        <v>3342</v>
-      </c>
       <c r="C7" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D7" t="s">
         <v>360</v>
@@ -40871,10 +40889,10 @@
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3346</v>
+        <v>3349</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3347</v>
+        <v>3350</v>
       </c>
       <c r="H7" s="38">
         <v>800</v>
@@ -40886,7 +40904,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3345</v>
+        <v>3348</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -40936,13 +40954,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3348</v>
+        <v>3351</v>
       </c>
       <c r="B8" t="s">
-        <v>3342</v>
+        <v>3345</v>
       </c>
       <c r="C8" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D8" t="s">
         <v>360</v>
@@ -40951,10 +40969,10 @@
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3349</v>
+        <v>3352</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3350</v>
+        <v>3353</v>
       </c>
       <c r="H8" s="38">
         <v>800</v>
@@ -40966,7 +40984,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3348</v>
+        <v>3351</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -41019,13 +41037,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3351</v>
+        <v>3354</v>
       </c>
       <c r="B9" t="s">
-        <v>3352</v>
+        <v>3355</v>
       </c>
       <c r="C9" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D9" t="s">
         <v>360</v>
@@ -41034,10 +41052,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3353</v>
+        <v>3356</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3354</v>
+        <v>3357</v>
       </c>
       <c r="H9" s="38">
         <v>1040</v>
@@ -41049,7 +41067,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3351</v>
+        <v>3354</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -41099,13 +41117,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>3358</v>
+      </c>
+      <c r="B10" t="s">
         <v>3355</v>
       </c>
-      <c r="B10" t="s">
-        <v>3352</v>
-      </c>
       <c r="C10" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D10" t="s">
         <v>360</v>
@@ -41114,10 +41132,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3356</v>
+        <v>3359</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3357</v>
+        <v>3360</v>
       </c>
       <c r="H10" s="38">
         <v>1040</v>
@@ -41129,7 +41147,7 @@
         <v>20</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3355</v>
+        <v>3358</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -41179,13 +41197,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3358</v>
+        <v>3361</v>
       </c>
       <c r="B11" t="s">
-        <v>3359</v>
+        <v>3362</v>
       </c>
       <c r="C11" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D11" t="s">
         <v>360</v>
@@ -41194,10 +41212,10 @@
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3360</v>
+        <v>3363</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3361</v>
+        <v>3364</v>
       </c>
       <c r="H11" s="38">
         <v>900</v>
@@ -41209,7 +41227,7 @@
         <v>5</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3358</v>
+        <v>3361</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -41242,7 +41260,7 @@
         <v>830</v>
       </c>
       <c r="AZ11" t="s">
-        <v>3362</v>
+        <v>3365</v>
       </c>
       <c r="BC11" t="s">
         <v>164</v>
@@ -41262,13 +41280,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3363</v>
+        <v>3366</v>
       </c>
       <c r="B12" t="s">
-        <v>3359</v>
+        <v>3362</v>
       </c>
       <c r="C12" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D12" t="s">
         <v>360</v>
@@ -41277,10 +41295,10 @@
         <v>70</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>3364</v>
+        <v>3367</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3365</v>
+        <v>3368</v>
       </c>
       <c r="H12" s="38">
         <v>900</v>
@@ -41292,7 +41310,7 @@
         <v>5</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3363</v>
+        <v>3366</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -41325,7 +41343,7 @@
         <v>830</v>
       </c>
       <c r="AZ12" t="s">
-        <v>3366</v>
+        <v>3369</v>
       </c>
       <c r="BC12" t="s">
         <v>164</v>
@@ -41345,13 +41363,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3367</v>
+        <v>3370</v>
       </c>
       <c r="B13" t="s">
-        <v>3359</v>
+        <v>3362</v>
       </c>
       <c r="C13" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D13" t="s">
         <v>360</v>
@@ -41360,10 +41378,10 @@
         <v>70</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>3368</v>
+        <v>3371</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3369</v>
+        <v>3372</v>
       </c>
       <c r="H13" s="38">
         <v>900</v>
@@ -41375,7 +41393,7 @@
         <v>5</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3367</v>
+        <v>3370</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -41405,7 +41423,7 @@
         <v>830</v>
       </c>
       <c r="AZ13" t="s">
-        <v>3370</v>
+        <v>3373</v>
       </c>
       <c r="BC13" t="s">
         <v>164</v>
@@ -43849,7 +43867,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV15"/>
+  <dimension ref="A1:BY15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -44092,16 +44110,25 @@
       <c r="BV1" s="41" t="s">
         <v>1846</v>
       </c>
+      <c r="BW1" s="41" t="s">
+        <v>3326</v>
+      </c>
+      <c r="BX1" s="41" t="s">
+        <v>3327</v>
+      </c>
+      <c r="BY1" s="41" t="s">
+        <v>3328</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3371</v>
+        <v>3374</v>
       </c>
       <c r="B2" t="s">
-        <v>3372</v>
+        <v>3375</v>
       </c>
       <c r="C2" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D2" t="s">
         <v>357</v>
@@ -44110,10 +44137,10 @@
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3373</v>
+        <v>3376</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3374</v>
+        <v>3377</v>
       </c>
       <c r="H2" s="38">
         <v>850</v>
@@ -44125,7 +44152,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3371</v>
+        <v>3374</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -44178,13 +44205,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>3378</v>
+      </c>
+      <c r="B3" t="s">
         <v>3375</v>
       </c>
-      <c r="B3" t="s">
-        <v>3372</v>
-      </c>
       <c r="C3" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D3" t="s">
         <v>357</v>
@@ -44193,10 +44220,10 @@
         <v>70</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>3373</v>
+        <v>3376</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3374</v>
+        <v>3377</v>
       </c>
       <c r="H3" s="38">
         <v>850</v>
@@ -44208,7 +44235,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3375</v>
+        <v>3378</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -44261,13 +44288,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3376</v>
+        <v>3379</v>
       </c>
       <c r="B4" t="s">
-        <v>3372</v>
+        <v>3375</v>
       </c>
       <c r="C4" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D4" t="s">
         <v>357</v>
@@ -44276,10 +44303,10 @@
         <v>70</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>3373</v>
+        <v>3376</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3374</v>
+        <v>3377</v>
       </c>
       <c r="H4" s="38">
         <v>850</v>
@@ -44291,7 +44318,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3376</v>
+        <v>3379</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -44344,13 +44371,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3377</v>
+        <v>3380</v>
       </c>
       <c r="B5" t="s">
-        <v>3372</v>
+        <v>3375</v>
       </c>
       <c r="C5" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D5" t="s">
         <v>357</v>
@@ -44359,10 +44386,10 @@
         <v>70</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>3373</v>
+        <v>3376</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3374</v>
+        <v>3377</v>
       </c>
       <c r="H5" s="38">
         <v>850</v>
@@ -44374,7 +44401,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3377</v>
+        <v>3380</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -44427,13 +44454,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3378</v>
+        <v>3381</v>
       </c>
       <c r="B6" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C6" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D6" t="s">
         <v>357</v>
@@ -44442,10 +44469,10 @@
         <v>70</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>3380</v>
+        <v>3383</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3381</v>
+        <v>3384</v>
       </c>
       <c r="H6" s="38">
         <v>1050</v>
@@ -44457,7 +44484,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3378</v>
+        <v>3381</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -44507,13 +44534,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B7" t="s">
         <v>3382</v>
       </c>
-      <c r="B7" t="s">
-        <v>3379</v>
-      </c>
       <c r="C7" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D7" t="s">
         <v>357</v>
@@ -44522,10 +44549,10 @@
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3380</v>
+        <v>3383</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3381</v>
+        <v>3384</v>
       </c>
       <c r="H7" s="38">
         <v>1050</v>
@@ -44537,7 +44564,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3382</v>
+        <v>3385</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -44587,13 +44614,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3383</v>
+        <v>3386</v>
       </c>
       <c r="B8" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C8" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D8" t="s">
         <v>357</v>
@@ -44602,10 +44629,10 @@
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3380</v>
+        <v>3383</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3381</v>
+        <v>3384</v>
       </c>
       <c r="H8" s="38">
         <v>1050</v>
@@ -44617,7 +44644,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3383</v>
+        <v>3386</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -44667,13 +44694,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3384</v>
+        <v>3387</v>
       </c>
       <c r="B9" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C9" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D9" t="s">
         <v>357</v>
@@ -44682,10 +44709,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3380</v>
+        <v>3383</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3381</v>
+        <v>3384</v>
       </c>
       <c r="H9" s="38">
         <v>1050</v>
@@ -44697,7 +44724,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3384</v>
+        <v>3387</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -44747,13 +44774,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3385</v>
+        <v>3388</v>
       </c>
       <c r="B10" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C10" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D10" t="s">
         <v>357</v>
@@ -44762,10 +44789,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3380</v>
+        <v>3383</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3381</v>
+        <v>3384</v>
       </c>
       <c r="H10" s="38">
         <v>1050</v>
@@ -44777,7 +44804,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3385</v>
+        <v>3388</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -44827,13 +44854,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3386</v>
+        <v>3389</v>
       </c>
       <c r="B11" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C11" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D11" t="s">
         <v>357</v>
@@ -44842,10 +44869,10 @@
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3387</v>
+        <v>3390</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3388</v>
+        <v>3391</v>
       </c>
       <c r="H11" s="38">
         <v>1050</v>
@@ -44857,7 +44884,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3386</v>
+        <v>3389</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -44907,13 +44934,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3389</v>
+        <v>3392</v>
       </c>
       <c r="B12" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C12" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D12" t="s">
         <v>357</v>
@@ -44922,10 +44949,10 @@
         <v>70</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>3387</v>
+        <v>3390</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3388</v>
+        <v>3391</v>
       </c>
       <c r="H12" s="38">
         <v>1050</v>
@@ -44937,7 +44964,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3389</v>
+        <v>3392</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -44987,13 +45014,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3390</v>
+        <v>3393</v>
       </c>
       <c r="B13" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C13" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D13" t="s">
         <v>357</v>
@@ -45002,10 +45029,10 @@
         <v>70</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>3387</v>
+        <v>3390</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3388</v>
+        <v>3391</v>
       </c>
       <c r="H13" s="38">
         <v>1050</v>
@@ -45017,7 +45044,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3390</v>
+        <v>3393</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -45067,13 +45094,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3391</v>
+        <v>3394</v>
       </c>
       <c r="B14" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C14" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D14" t="s">
         <v>357</v>
@@ -45082,10 +45109,10 @@
         <v>70</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>3387</v>
+        <v>3390</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>3388</v>
+        <v>3391</v>
       </c>
       <c r="H14" s="38">
         <v>1050</v>
@@ -45097,7 +45124,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>3391</v>
+        <v>3394</v>
       </c>
       <c r="L14" s="39">
         <v>10</v>
@@ -45147,13 +45174,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3392</v>
+        <v>3395</v>
       </c>
       <c r="B15" t="s">
-        <v>3379</v>
+        <v>3382</v>
       </c>
       <c r="C15" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D15" t="s">
         <v>357</v>
@@ -45162,10 +45189,10 @@
         <v>70</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>3387</v>
+        <v>3390</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>3388</v>
+        <v>3391</v>
       </c>
       <c r="H15" s="38">
         <v>1050</v>
@@ -45177,7 +45204,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>3392</v>
+        <v>3395</v>
       </c>
       <c r="L15" s="39">
         <v>10</v>
@@ -47651,7 +47678,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV16"/>
+  <dimension ref="A1:BY16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -47894,16 +47921,25 @@
       <c r="BV1" s="41" t="s">
         <v>1846</v>
       </c>
+      <c r="BW1" s="41" t="s">
+        <v>3326</v>
+      </c>
+      <c r="BX1" s="41" t="s">
+        <v>3327</v>
+      </c>
+      <c r="BY1" s="41" t="s">
+        <v>3328</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3393</v>
+        <v>3396</v>
       </c>
       <c r="B2" t="s">
-        <v>3394</v>
+        <v>3397</v>
       </c>
       <c r="C2" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -47915,7 +47951,7 @@
         <v>183</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3395</v>
+        <v>3398</v>
       </c>
       <c r="H2" s="38">
         <v>799</v>
@@ -47927,7 +47963,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3393</v>
+        <v>3396</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -47980,13 +48016,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3396</v>
+        <v>3399</v>
       </c>
       <c r="B3" t="s">
-        <v>3394</v>
+        <v>3397</v>
       </c>
       <c r="C3" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -47998,7 +48034,7 @@
         <v>183</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3395</v>
+        <v>3398</v>
       </c>
       <c r="H3" s="38">
         <v>799</v>
@@ -48010,7 +48046,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3396</v>
+        <v>3399</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -48063,13 +48099,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>3400</v>
+      </c>
+      <c r="B4" t="s">
         <v>3397</v>
       </c>
-      <c r="B4" t="s">
-        <v>3394</v>
-      </c>
       <c r="C4" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -48081,7 +48117,7 @@
         <v>183</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3395</v>
+        <v>3398</v>
       </c>
       <c r="H4" s="38">
         <v>799</v>
@@ -48093,7 +48129,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3397</v>
+        <v>3400</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -48146,13 +48182,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3398</v>
+        <v>3401</v>
       </c>
       <c r="B5" t="s">
-        <v>3394</v>
+        <v>3397</v>
       </c>
       <c r="C5" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -48164,7 +48200,7 @@
         <v>183</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3395</v>
+        <v>3398</v>
       </c>
       <c r="H5" s="38">
         <v>799</v>
@@ -48176,7 +48212,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3398</v>
+        <v>3401</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -48229,13 +48265,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3399</v>
+        <v>3402</v>
       </c>
       <c r="B6" t="s">
-        <v>3394</v>
+        <v>3397</v>
       </c>
       <c r="C6" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -48247,7 +48283,7 @@
         <v>183</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3395</v>
+        <v>3398</v>
       </c>
       <c r="H6" s="38">
         <v>799</v>
@@ -48259,7 +48295,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3399</v>
+        <v>3402</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -48312,13 +48348,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3400</v>
+        <v>3403</v>
       </c>
       <c r="B7" t="s">
-        <v>3401</v>
+        <v>3404</v>
       </c>
       <c r="C7" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -48327,10 +48363,10 @@
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="H7" s="38">
         <v>785</v>
@@ -48342,7 +48378,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3400</v>
+        <v>3403</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -48395,13 +48431,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>3407</v>
+      </c>
+      <c r="B8" t="s">
         <v>3404</v>
       </c>
-      <c r="B8" t="s">
-        <v>3401</v>
-      </c>
       <c r="C8" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -48410,10 +48446,10 @@
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="H8" s="38">
         <v>785</v>
@@ -48425,7 +48461,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3404</v>
+        <v>3407</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -48478,13 +48514,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3405</v>
+        <v>3408</v>
       </c>
       <c r="B9" t="s">
-        <v>3401</v>
+        <v>3404</v>
       </c>
       <c r="C9" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -48493,10 +48529,10 @@
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="H9" s="38">
         <v>785</v>
@@ -48508,7 +48544,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3405</v>
+        <v>3408</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -48561,13 +48597,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3406</v>
+        <v>3409</v>
       </c>
       <c r="B10" t="s">
-        <v>3401</v>
+        <v>3404</v>
       </c>
       <c r="C10" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D10" t="s">
         <v>333</v>
@@ -48576,10 +48612,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="H10" s="38">
         <v>785</v>
@@ -48591,7 +48627,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3406</v>
+        <v>3409</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -48644,13 +48680,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3407</v>
+        <v>3410</v>
       </c>
       <c r="B11" t="s">
-        <v>3401</v>
+        <v>3404</v>
       </c>
       <c r="C11" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D11" t="s">
         <v>333</v>
@@ -48659,10 +48695,10 @@
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="H11" s="38">
         <v>785</v>
@@ -48674,7 +48710,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3407</v>
+        <v>3410</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -48727,13 +48763,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3408</v>
+        <v>3411</v>
       </c>
       <c r="B12" t="s">
-        <v>3409</v>
+        <v>3412</v>
       </c>
       <c r="C12" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D12" t="s">
         <v>333</v>
@@ -48745,7 +48781,7 @@
         <v>265</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3410</v>
+        <v>3413</v>
       </c>
       <c r="H12" s="38">
         <v>800</v>
@@ -48757,7 +48793,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3408</v>
+        <v>3411</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -48807,13 +48843,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3411</v>
+        <v>3414</v>
       </c>
       <c r="B13" t="s">
-        <v>3409</v>
+        <v>3412</v>
       </c>
       <c r="C13" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D13" t="s">
         <v>333</v>
@@ -48825,7 +48861,7 @@
         <v>265</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3410</v>
+        <v>3413</v>
       </c>
       <c r="H13" s="38">
         <v>800</v>
@@ -48837,7 +48873,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3411</v>
+        <v>3414</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -48887,13 +48923,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>3415</v>
+      </c>
+      <c r="B14" t="s">
         <v>3412</v>
       </c>
-      <c r="B14" t="s">
-        <v>3409</v>
-      </c>
       <c r="C14" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D14" t="s">
         <v>333</v>
@@ -48905,7 +48941,7 @@
         <v>265</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>3410</v>
+        <v>3413</v>
       </c>
       <c r="H14" s="38">
         <v>800</v>
@@ -48917,7 +48953,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>3412</v>
+        <v>3415</v>
       </c>
       <c r="L14" s="39">
         <v>10</v>
@@ -48967,13 +49003,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3413</v>
+        <v>3416</v>
       </c>
       <c r="B15" t="s">
-        <v>3409</v>
+        <v>3412</v>
       </c>
       <c r="C15" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D15" t="s">
         <v>333</v>
@@ -48985,7 +49021,7 @@
         <v>265</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>3410</v>
+        <v>3413</v>
       </c>
       <c r="H15" s="38">
         <v>800</v>
@@ -48997,7 +49033,7 @@
         <v>2</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>3413</v>
+        <v>3416</v>
       </c>
       <c r="L15" s="39">
         <v>10</v>
@@ -49047,13 +49083,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3414</v>
+        <v>3417</v>
       </c>
       <c r="B16" t="s">
-        <v>3409</v>
+        <v>3412</v>
       </c>
       <c r="C16" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D16" t="s">
         <v>333</v>
@@ -49065,7 +49101,7 @@
         <v>265</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>3410</v>
+        <v>3413</v>
       </c>
       <c r="H16" s="38">
         <v>800</v>
@@ -49077,7 +49113,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>3414</v>
+        <v>3417</v>
       </c>
       <c r="L16" s="39">
         <v>10</v>
@@ -51551,7 +51587,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV19"/>
+  <dimension ref="A1:BY19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -51794,28 +51830,37 @@
       <c r="BV1" s="41" t="s">
         <v>1846</v>
       </c>
+      <c r="BW1" s="41" t="s">
+        <v>3326</v>
+      </c>
+      <c r="BX1" s="41" t="s">
+        <v>3327</v>
+      </c>
+      <c r="BY1" s="41" t="s">
+        <v>3328</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3415</v>
+        <v>3418</v>
       </c>
       <c r="B2" t="s">
-        <v>3416</v>
+        <v>3419</v>
       </c>
       <c r="C2" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D2" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3419</v>
+        <v>3422</v>
       </c>
       <c r="H2" s="38">
         <v>500</v>
@@ -51827,7 +51872,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3415</v>
+        <v>3418</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -51877,25 +51922,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>3423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3419</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D3" t="s">
         <v>3420</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3416</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3328</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3417</v>
       </c>
       <c r="E3" t="s">
         <v>70</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3419</v>
+        <v>3422</v>
       </c>
       <c r="H3" s="38">
         <v>500</v>
@@ -51907,7 +51952,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3420</v>
+        <v>3423</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -51957,25 +52002,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3421</v>
+        <v>3424</v>
       </c>
       <c r="B4" t="s">
-        <v>3416</v>
+        <v>3419</v>
       </c>
       <c r="C4" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D4" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E4" t="s">
         <v>70</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3419</v>
+        <v>3422</v>
       </c>
       <c r="H4" s="38">
         <v>500</v>
@@ -51987,7 +52032,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3421</v>
+        <v>3424</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -52037,25 +52082,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3422</v>
+        <v>3425</v>
       </c>
       <c r="B5" t="s">
-        <v>3416</v>
+        <v>3419</v>
       </c>
       <c r="C5" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D5" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E5" t="s">
         <v>70</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3419</v>
+        <v>3422</v>
       </c>
       <c r="H5" s="38">
         <v>500</v>
@@ -52067,7 +52112,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3422</v>
+        <v>3425</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -52117,25 +52162,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3423</v>
+        <v>3426</v>
       </c>
       <c r="B6" t="s">
-        <v>3416</v>
+        <v>3419</v>
       </c>
       <c r="C6" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D6" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E6" t="s">
         <v>70</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3419</v>
+        <v>3422</v>
       </c>
       <c r="H6" s="38">
         <v>500</v>
@@ -52147,7 +52192,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3423</v>
+        <v>3426</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -52197,25 +52242,25 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3424</v>
+        <v>3427</v>
       </c>
       <c r="B7" t="s">
-        <v>3416</v>
+        <v>3419</v>
       </c>
       <c r="C7" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D7" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E7" t="s">
         <v>70</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3419</v>
+        <v>3422</v>
       </c>
       <c r="H7" s="38">
         <v>500</v>
@@ -52227,7 +52272,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3424</v>
+        <v>3427</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -52277,25 +52322,25 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3425</v>
+        <v>3428</v>
       </c>
       <c r="B8" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C8" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D8" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E8" t="s">
         <v>70</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>3427</v>
+        <v>3430</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3428</v>
+        <v>3431</v>
       </c>
       <c r="H8" s="38">
         <v>500</v>
@@ -52307,7 +52352,7 @@
         <v>2</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3425</v>
+        <v>3428</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -52351,25 +52396,25 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>3432</v>
+      </c>
+      <c r="B9" t="s">
         <v>3429</v>
       </c>
-      <c r="B9" t="s">
-        <v>3426</v>
-      </c>
       <c r="C9" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D9" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E9" t="s">
         <v>70</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>3427</v>
+        <v>3430</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3428</v>
+        <v>3431</v>
       </c>
       <c r="H9" s="38">
         <v>500</v>
@@ -52381,7 +52426,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3429</v>
+        <v>3432</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -52425,25 +52470,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3430</v>
+        <v>3433</v>
       </c>
       <c r="B10" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C10" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D10" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E10" t="s">
         <v>70</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>3427</v>
+        <v>3430</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>3428</v>
+        <v>3431</v>
       </c>
       <c r="H10" s="38">
         <v>500</v>
@@ -52455,7 +52500,7 @@
         <v>2</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>3430</v>
+        <v>3433</v>
       </c>
       <c r="L10" s="39">
         <v>10</v>
@@ -52499,25 +52544,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3431</v>
+        <v>3434</v>
       </c>
       <c r="B11" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C11" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D11" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E11" t="s">
         <v>70</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>3427</v>
+        <v>3430</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>3428</v>
+        <v>3431</v>
       </c>
       <c r="H11" s="38">
         <v>500</v>
@@ -52529,7 +52574,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>3431</v>
+        <v>3434</v>
       </c>
       <c r="L11" s="39">
         <v>10</v>
@@ -52573,25 +52618,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3432</v>
+        <v>3435</v>
       </c>
       <c r="B12" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C12" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D12" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E12" t="s">
         <v>70</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>3427</v>
+        <v>3430</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>3428</v>
+        <v>3431</v>
       </c>
       <c r="H12" s="38">
         <v>500</v>
@@ -52603,7 +52648,7 @@
         <v>2</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>3432</v>
+        <v>3435</v>
       </c>
       <c r="L12" s="39">
         <v>10</v>
@@ -52647,25 +52692,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3433</v>
+        <v>3436</v>
       </c>
       <c r="B13" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C13" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D13" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E13" t="s">
         <v>70</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>3427</v>
+        <v>3430</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>3428</v>
+        <v>3431</v>
       </c>
       <c r="H13" s="38">
         <v>500</v>
@@ -52677,7 +52722,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>3433</v>
+        <v>3436</v>
       </c>
       <c r="L13" s="39">
         <v>10</v>
@@ -52721,25 +52766,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3434</v>
+        <v>3437</v>
       </c>
       <c r="B14" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C14" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D14" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E14" t="s">
         <v>70</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>3435</v>
+        <v>3438</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>3436</v>
+        <v>3439</v>
       </c>
       <c r="H14" s="38">
         <v>550</v>
@@ -52751,7 +52796,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>3434</v>
+        <v>3437</v>
       </c>
       <c r="L14" s="39">
         <v>10</v>
@@ -52801,25 +52846,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3437</v>
+        <v>3440</v>
       </c>
       <c r="B15" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C15" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D15" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E15" t="s">
         <v>70</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>3435</v>
+        <v>3438</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>3436</v>
+        <v>3439</v>
       </c>
       <c r="H15" s="38">
         <v>550</v>
@@ -52831,7 +52876,7 @@
         <v>2</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>3437</v>
+        <v>3440</v>
       </c>
       <c r="L15" s="39">
         <v>10</v>
@@ -52881,25 +52926,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3438</v>
+        <v>3441</v>
       </c>
       <c r="B16" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C16" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D16" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E16" t="s">
         <v>70</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>3435</v>
+        <v>3438</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>3436</v>
+        <v>3439</v>
       </c>
       <c r="H16" s="38">
         <v>550</v>
@@ -52911,7 +52956,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>3438</v>
+        <v>3441</v>
       </c>
       <c r="L16" s="39">
         <v>10</v>
@@ -52961,25 +53006,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3439</v>
+        <v>3442</v>
       </c>
       <c r="B17" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C17" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D17" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E17" t="s">
         <v>70</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>3435</v>
+        <v>3438</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>3436</v>
+        <v>3439</v>
       </c>
       <c r="H17" s="38">
         <v>550</v>
@@ -52991,7 +53036,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>3439</v>
+        <v>3442</v>
       </c>
       <c r="L17" s="39">
         <v>10</v>
@@ -53041,25 +53086,25 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3440</v>
+        <v>3443</v>
       </c>
       <c r="B18" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C18" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D18" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E18" t="s">
         <v>70</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>3435</v>
+        <v>3438</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>3436</v>
+        <v>3439</v>
       </c>
       <c r="H18" s="38">
         <v>550</v>
@@ -53071,7 +53116,7 @@
         <v>2</v>
       </c>
       <c r="K18" s="39" t="s">
-        <v>3440</v>
+        <v>3443</v>
       </c>
       <c r="L18" s="39">
         <v>10</v>
@@ -53121,25 +53166,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3441</v>
+        <v>3444</v>
       </c>
       <c r="B19" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="C19" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D19" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="E19" t="s">
         <v>70</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>3435</v>
+        <v>3438</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>3436</v>
+        <v>3439</v>
       </c>
       <c r="H19" s="38">
         <v>550</v>
@@ -53151,7 +53196,7 @@
         <v>2</v>
       </c>
       <c r="K19" s="39" t="s">
-        <v>3441</v>
+        <v>3444</v>
       </c>
       <c r="L19" s="39">
         <v>10</v>
@@ -55625,7 +55670,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV5"/>
+  <dimension ref="A1:BY5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -55868,16 +55913,25 @@
       <c r="BV1" s="41" t="s">
         <v>1846</v>
       </c>
+      <c r="BW1" s="41" t="s">
+        <v>3326</v>
+      </c>
+      <c r="BX1" s="41" t="s">
+        <v>3327</v>
+      </c>
+      <c r="BY1" s="41" t="s">
+        <v>3328</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3442</v>
+        <v>3445</v>
       </c>
       <c r="B2" t="s">
-        <v>3443</v>
+        <v>3446</v>
       </c>
       <c r="C2" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D2" t="s">
         <v>375</v>
@@ -55889,7 +55943,7 @@
         <v>361</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3444</v>
+        <v>3447</v>
       </c>
       <c r="H2" s="38">
         <v>250</v>
@@ -55901,7 +55955,7 @@
         <v>8</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3442</v>
+        <v>3445</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -55951,13 +56005,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3445</v>
+        <v>3448</v>
       </c>
       <c r="B3" t="s">
-        <v>3443</v>
+        <v>3446</v>
       </c>
       <c r="C3" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D3" t="s">
         <v>375</v>
@@ -55969,7 +56023,7 @@
         <v>361</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3444</v>
+        <v>3447</v>
       </c>
       <c r="H3" s="38">
         <v>250</v>
@@ -55981,7 +56035,7 @@
         <v>8</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3445</v>
+        <v>3448</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -56031,13 +56085,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>3449</v>
+      </c>
+      <c r="B4" t="s">
         <v>3446</v>
       </c>
-      <c r="B4" t="s">
-        <v>3443</v>
-      </c>
       <c r="C4" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D4" t="s">
         <v>375</v>
@@ -56049,7 +56103,7 @@
         <v>361</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3444</v>
+        <v>3447</v>
       </c>
       <c r="H4" s="38">
         <v>250</v>
@@ -56061,7 +56115,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3446</v>
+        <v>3449</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -56111,13 +56165,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3447</v>
+        <v>3450</v>
       </c>
       <c r="B5" t="s">
-        <v>3443</v>
+        <v>3446</v>
       </c>
       <c r="C5" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D5" t="s">
         <v>375</v>
@@ -56129,7 +56183,7 @@
         <v>361</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3444</v>
+        <v>3447</v>
       </c>
       <c r="H5" s="38">
         <v>250</v>
@@ -56141,7 +56195,7 @@
         <v>8</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3447</v>
+        <v>3450</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -58615,7 +58669,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV9"/>
+  <dimension ref="A1:BY9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -58858,16 +58912,25 @@
       <c r="BV1" s="41" t="s">
         <v>1846</v>
       </c>
+      <c r="BW1" s="41" t="s">
+        <v>3326</v>
+      </c>
+      <c r="BX1" s="41" t="s">
+        <v>3327</v>
+      </c>
+      <c r="BY1" s="41" t="s">
+        <v>3328</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3448</v>
+        <v>3451</v>
       </c>
       <c r="B2" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="C2" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D2" t="s">
         <v>349</v>
@@ -58879,7 +58942,7 @@
         <v>520</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3450</v>
+        <v>3453</v>
       </c>
       <c r="H2" s="38">
         <v>1600</v>
@@ -58891,7 +58954,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3448</v>
+        <v>3451</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -58941,13 +59004,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3451</v>
+        <v>3454</v>
       </c>
       <c r="B3" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="C3" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D3" t="s">
         <v>349</v>
@@ -58959,7 +59022,7 @@
         <v>520</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3450</v>
+        <v>3453</v>
       </c>
       <c r="H3" s="38">
         <v>1600</v>
@@ -58971,7 +59034,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3451</v>
+        <v>3454</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -59021,13 +59084,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>3455</v>
+      </c>
+      <c r="B4" t="s">
         <v>3452</v>
       </c>
-      <c r="B4" t="s">
-        <v>3449</v>
-      </c>
       <c r="C4" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D4" t="s">
         <v>349</v>
@@ -59039,7 +59102,7 @@
         <v>520</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>3450</v>
+        <v>3453</v>
       </c>
       <c r="H4" s="38">
         <v>1600</v>
@@ -59051,7 +59114,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="39" t="s">
-        <v>3452</v>
+        <v>3455</v>
       </c>
       <c r="L4" s="39">
         <v>10</v>
@@ -59101,13 +59164,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3453</v>
+        <v>3456</v>
       </c>
       <c r="B5" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="C5" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D5" t="s">
         <v>349</v>
@@ -59119,7 +59182,7 @@
         <v>520</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>3450</v>
+        <v>3453</v>
       </c>
       <c r="H5" s="38">
         <v>1600</v>
@@ -59131,7 +59194,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>3453</v>
+        <v>3456</v>
       </c>
       <c r="L5" s="39">
         <v>10</v>
@@ -59181,13 +59244,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3454</v>
+        <v>3457</v>
       </c>
       <c r="B6" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="C6" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D6" t="s">
         <v>349</v>
@@ -59199,7 +59262,7 @@
         <v>533</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>3455</v>
+        <v>3458</v>
       </c>
       <c r="H6" s="38">
         <v>1600</v>
@@ -59211,7 +59274,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>3454</v>
+        <v>3457</v>
       </c>
       <c r="L6" s="39">
         <v>10</v>
@@ -59264,13 +59327,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3456</v>
+        <v>3459</v>
       </c>
       <c r="B7" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="C7" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D7" t="s">
         <v>349</v>
@@ -59282,7 +59345,7 @@
         <v>533</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>3455</v>
+        <v>3458</v>
       </c>
       <c r="H7" s="38">
         <v>1600</v>
@@ -59294,7 +59357,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>3456</v>
+        <v>3459</v>
       </c>
       <c r="L7" s="39">
         <v>10</v>
@@ -59347,13 +59410,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3457</v>
+        <v>3460</v>
       </c>
       <c r="B8" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="C8" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D8" t="s">
         <v>349</v>
@@ -59365,7 +59428,7 @@
         <v>533</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>3455</v>
+        <v>3458</v>
       </c>
       <c r="H8" s="38">
         <v>1600</v>
@@ -59377,7 +59440,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>3457</v>
+        <v>3460</v>
       </c>
       <c r="L8" s="39">
         <v>10</v>
@@ -59430,13 +59493,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3458</v>
+        <v>3461</v>
       </c>
       <c r="B9" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="C9" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D9" t="s">
         <v>349</v>
@@ -59448,7 +59511,7 @@
         <v>533</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>3455</v>
+        <v>3458</v>
       </c>
       <c r="H9" s="38">
         <v>1600</v>
@@ -59460,7 +59523,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>3458</v>
+        <v>3461</v>
       </c>
       <c r="L9" s="39">
         <v>10</v>
@@ -61937,7 +62000,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV3"/>
+  <dimension ref="A1:BY3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -62180,28 +62243,37 @@
       <c r="BV1" s="41" t="s">
         <v>1846</v>
       </c>
+      <c r="BW1" s="41" t="s">
+        <v>3326</v>
+      </c>
+      <c r="BX1" s="41" t="s">
+        <v>3327</v>
+      </c>
+      <c r="BY1" s="41" t="s">
+        <v>3328</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3459</v>
+        <v>3462</v>
       </c>
       <c r="B2" t="s">
-        <v>3460</v>
+        <v>3463</v>
       </c>
       <c r="C2" t="s">
-        <v>3328</v>
+        <v>3331</v>
       </c>
       <c r="D2" t="s">
-        <v>3461</v>
+        <v>3464</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>3462</v>
+        <v>3465</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>3463</v>
+        <v>3466</v>
       </c>
       <c r="H2" s="38">
         <v>1000</v>
@@ -62213,7 +62285,7 @@
         <v>5</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>3459</v>
+        <v>3462</v>
       </c>
       <c r="L2" s="39">
         <v>10</v>
@@ -62254,28 +62326,31 @@
       <c r="BL2" t="s">
         <v>164</v>
       </c>
+      <c r="BW2" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>3467</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3463</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D3" t="s">
         <v>3464</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3460</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3328</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3461</v>
       </c>
       <c r="E3" t="s">
         <v>70</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>3465</v>
+        <v>3468</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>3466</v>
+        <v>3469</v>
       </c>
       <c r="H3" s="38">
         <v>1000</v>
@@ -62287,7 +62362,7 @@
         <v>5</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>3464</v>
+        <v>3467</v>
       </c>
       <c r="L3" s="39">
         <v>10</v>
@@ -62327,6 +62402,9 @@
       </c>
       <c r="BL3" t="s">
         <v>164</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>
